--- a/raw/time_tables/BCA(bca-62)/1/1.xlsx
+++ b/raw/time_tables/BCA(bca-62)/1/1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\neetu.singh\Desktop\new CD created\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\neetu.singh\Desktop\Time table odd 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DC80539F-75F4-462A-BF14-1A624FC2C97E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2315D46-7684-4E25-82CA-3E80F0F9B70C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9405" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="BCA I semester 2026" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -175,9 +174,6 @@
     <t>Dr.Himani</t>
   </si>
   <si>
-    <t>TBCA(25B11CA111)-NET/TR305</t>
-  </si>
-  <si>
     <t>TBCA1(23B31MA111)-HPT/TR524</t>
   </si>
   <si>
@@ -226,49 +222,52 @@
     <t>LBCA1(25B11CA111)-SNA/CR501</t>
   </si>
   <si>
-    <t>TBCA(25B11CA111)-SNA/TR305</t>
+    <t>SNA Sharma</t>
+  </si>
+  <si>
+    <t>Dr.Neetu/Dr.Sandeep/SNA</t>
+  </si>
+  <si>
+    <t>VSH Shukla</t>
+  </si>
+  <si>
+    <t>SHW Sharma</t>
+  </si>
+  <si>
+    <t>Ms.Avantika</t>
+  </si>
+  <si>
+    <t>Sonia/Dr.Neetu</t>
+  </si>
+  <si>
+    <t>LBCA1(25B11CA112)-SHW/CR501</t>
+  </si>
+  <si>
+    <t>LBCA1(25B11CA113)-VSH/CR501</t>
+  </si>
+  <si>
+    <t>LBCA1(25B11CA114)-NF7/CR501</t>
+  </si>
+  <si>
+    <t>NF7</t>
+  </si>
+  <si>
+    <t>PBCA11(25B15CA112)-(SHW/Komal)/CC2421</t>
   </si>
   <si>
     <t>PBCA11(25B15CA111)-(NET,SNA)/CC3423</t>
   </si>
   <si>
-    <t>SNA Sharma</t>
-  </si>
-  <si>
-    <t>Dr.Neetu/Dr.Sandeep/SNA</t>
-  </si>
-  <si>
-    <t>LBCA1(25B11CA112)-VSH/CR501</t>
-  </si>
-  <si>
-    <t>PBCA11(25B15CA112)-(VSH)/CC2421</t>
-  </si>
-  <si>
-    <t>VSH Shukla</t>
-  </si>
-  <si>
-    <t>LBCA1(25B11CA113)-SHW/CR501</t>
-  </si>
-  <si>
-    <t>PBCA12(25B15CA112)-(SHW)/CC3423</t>
-  </si>
-  <si>
-    <t>SHW Sharma</t>
-  </si>
-  <si>
-    <t>Ms.Avantika</t>
-  </si>
-  <si>
-    <t>AVK</t>
-  </si>
-  <si>
-    <t>PBCA12(25B15CA111)-(SKS,DEP)/CC2421</t>
-  </si>
-  <si>
-    <t>LBCA1(25B11CA114)-AVK/CR501</t>
-  </si>
-  <si>
-    <t>Sonia/Dr.Neetu</t>
+    <t>PBCA12(25B15CA111)-(SKS,Deepika)/CC2421</t>
+  </si>
+  <si>
+    <t>TBCA11(25B11CA111)-SNA/TR305</t>
+  </si>
+  <si>
+    <t>TBCA12(25B11CA111)-NET/TR305</t>
+  </si>
+  <si>
+    <t>PBCA12(25B15CA112)-(SHW/NF7/Rekha)/CC3423</t>
   </si>
 </sst>
 </file>
@@ -507,7 +506,7 @@
       <name val="&quot;Times New Roman&quot;"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -562,6 +561,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="28">
     <border>
@@ -918,7 +923,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="127">
+  <cellXfs count="131">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1170,8 +1175,23 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1179,69 +1199,64 @@
     <xf numFmtId="0" fontId="17" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1522,17 +1537,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="21" customHeight="1">
-      <c r="A1" s="122" t="s">
+      <c r="A1" s="103" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="122"/>
-      <c r="C1" s="122"/>
-      <c r="D1" s="122"/>
-      <c r="E1" s="122"/>
-      <c r="F1" s="122"/>
-      <c r="G1" s="122"/>
-      <c r="H1" s="122"/>
-      <c r="I1" s="122"/>
+      <c r="B1" s="103"/>
+      <c r="C1" s="103"/>
+      <c r="D1" s="103"/>
+      <c r="E1" s="103"/>
+      <c r="F1" s="103"/>
+      <c r="G1" s="103"/>
+      <c r="H1" s="103"/>
+      <c r="I1" s="103"/>
       <c r="J1" s="18"/>
       <c r="K1" s="18"/>
       <c r="L1" s="18"/>
@@ -1550,17 +1565,17 @@
       <c r="X1" s="18"/>
     </row>
     <row r="2" spans="1:24" ht="21" customHeight="1">
-      <c r="A2" s="123" t="s">
+      <c r="A2" s="104" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="123"/>
-      <c r="C2" s="123"/>
-      <c r="D2" s="123"/>
-      <c r="E2" s="123"/>
-      <c r="F2" s="123"/>
-      <c r="G2" s="123"/>
-      <c r="H2" s="123"/>
-      <c r="I2" s="123"/>
+      <c r="B2" s="104"/>
+      <c r="C2" s="104"/>
+      <c r="D2" s="104"/>
+      <c r="E2" s="104"/>
+      <c r="F2" s="104"/>
+      <c r="G2" s="104"/>
+      <c r="H2" s="104"/>
+      <c r="I2" s="104"/>
       <c r="J2" s="18"/>
       <c r="K2" s="18"/>
       <c r="L2" s="18"/>
@@ -1605,38 +1620,38 @@
       </c>
     </row>
     <row r="4" spans="1:24" ht="68.25" customHeight="1">
-      <c r="A4" s="124" t="s">
+      <c r="A4" s="105" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="100" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C4" s="97" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D4" s="94" t="s">
-        <v>58</v>
-      </c>
-      <c r="E4" s="111"/>
+        <v>57</v>
+      </c>
+      <c r="E4" s="107"/>
       <c r="F4" s="96" t="s">
         <v>25</v>
       </c>
       <c r="G4" s="95" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H4" s="102"/>
-      <c r="I4" s="103" t="s">
-        <v>65</v>
+      <c r="I4" s="127" t="s">
+        <v>64</v>
       </c>
       <c r="J4" s="27"/>
       <c r="K4" s="27"/>
     </row>
     <row r="5" spans="1:24" ht="67.5" customHeight="1">
-      <c r="A5" s="114"/>
+      <c r="A5" s="106"/>
       <c r="B5" s="68"/>
       <c r="C5" s="68"/>
       <c r="D5" s="68"/>
-      <c r="E5" s="112"/>
+      <c r="E5" s="108"/>
       <c r="F5" s="87"/>
       <c r="G5" s="73"/>
       <c r="H5" s="69"/>
@@ -1661,30 +1676,30 @@
       <c r="A7" s="113" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="125" t="s">
-        <v>55</v>
-      </c>
-      <c r="C7" s="126"/>
+      <c r="B7" s="109" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" s="110"/>
       <c r="D7" s="95" t="s">
-        <v>57</v>
-      </c>
-      <c r="E7" s="120"/>
+        <v>56</v>
+      </c>
+      <c r="E7" s="119"/>
       <c r="F7" s="96" t="s">
         <v>25</v>
       </c>
       <c r="G7" s="98" t="s">
-        <v>66</v>
-      </c>
-      <c r="H7" s="109" t="s">
         <v>78</v>
       </c>
-      <c r="I7" s="110"/>
+      <c r="H7" s="111" t="s">
+        <v>77</v>
+      </c>
+      <c r="I7" s="112"/>
       <c r="K7" s="27"/>
     </row>
     <row r="8" spans="1:24" ht="60" customHeight="1">
-      <c r="A8" s="114"/>
+      <c r="A8" s="106"/>
       <c r="D8" s="83"/>
-      <c r="E8" s="121"/>
+      <c r="E8" s="120"/>
       <c r="F8" s="79"/>
       <c r="G8" s="71"/>
       <c r="H8" s="5"/>
@@ -1706,37 +1721,36 @@
       <c r="K9" s="27"/>
     </row>
     <row r="10" spans="1:24" ht="60.75" customHeight="1">
-      <c r="A10" s="106" t="s">
+      <c r="A10" s="117" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="97" t="s">
+      <c r="D10" s="98" t="s">
         <v>79</v>
-      </c>
-      <c r="D10" s="98" t="s">
-        <v>49</v>
       </c>
       <c r="E10" s="88"/>
       <c r="F10" s="96" t="s">
-        <v>50</v>
-      </c>
-      <c r="G10" s="109" t="s">
-        <v>67</v>
-      </c>
-      <c r="H10" s="110"/>
-      <c r="I10" s="68"/>
+        <v>49</v>
+      </c>
+      <c r="G10" s="111" t="s">
+        <v>76</v>
+      </c>
+      <c r="H10" s="112"/>
+      <c r="I10" s="126" t="s">
+        <v>73</v>
+      </c>
       <c r="J10" s="27"/>
       <c r="K10" s="27"/>
     </row>
     <row r="11" spans="1:24" ht="56.25" customHeight="1">
-      <c r="A11" s="107"/>
+      <c r="A11" s="118"/>
       <c r="B11" s="83"/>
       <c r="C11" s="84"/>
       <c r="D11" s="70"/>
       <c r="E11" s="89"/>
       <c r="F11" s="79"/>
       <c r="G11" s="70"/>
-      <c r="H11" s="115"/>
-      <c r="I11" s="116"/>
+      <c r="H11" s="124"/>
+      <c r="I11" s="125"/>
       <c r="J11" s="27"/>
       <c r="K11" s="27"/>
     </row>
@@ -1758,34 +1772,34 @@
         <v>12</v>
       </c>
       <c r="B13" s="97" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C13" s="100" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D13" s="97" t="s">
-        <v>79</v>
-      </c>
-      <c r="E13" s="111"/>
+        <v>73</v>
+      </c>
+      <c r="E13" s="107"/>
       <c r="F13" s="96" t="s">
-        <v>50</v>
-      </c>
-      <c r="H13" s="104" t="s">
-        <v>56</v>
-      </c>
-      <c r="I13" s="105"/>
+        <v>49</v>
+      </c>
+      <c r="H13" s="109" t="s">
+        <v>55</v>
+      </c>
+      <c r="I13" s="110"/>
       <c r="J13" s="27"/>
       <c r="K13" s="27"/>
     </row>
     <row r="14" spans="1:24" ht="46.5" customHeight="1">
-      <c r="A14" s="114"/>
+      <c r="A14" s="106"/>
       <c r="B14" s="68"/>
       <c r="D14" s="70"/>
-      <c r="E14" s="112"/>
+      <c r="E14" s="108"/>
       <c r="F14" s="79"/>
       <c r="G14" s="68"/>
-      <c r="H14" s="109"/>
-      <c r="I14" s="110"/>
+      <c r="H14" s="111"/>
+      <c r="I14" s="112"/>
       <c r="J14" s="27"/>
       <c r="K14" s="27"/>
     </row>
@@ -1803,46 +1817,45 @@
       <c r="K15" s="27"/>
     </row>
     <row r="16" spans="1:24" ht="63.75" customHeight="1">
-      <c r="A16" s="106" t="s">
+      <c r="A16" s="117" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="109" t="s">
-        <v>71</v>
-      </c>
-      <c r="C16" s="110"/>
+      <c r="B16" s="121" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" s="122"/>
       <c r="E16" s="80"/>
-      <c r="F16" s="74"/>
-      <c r="G16" s="103" t="s">
-        <v>65</v>
+      <c r="F16" s="127" t="s">
+        <v>64</v>
       </c>
       <c r="I16" s="73"/>
       <c r="J16" s="27"/>
       <c r="K16" s="27"/>
     </row>
     <row r="17" spans="1:11" ht="63.75" customHeight="1">
-      <c r="A17" s="108"/>
-      <c r="B17" s="109" t="s">
-        <v>74</v>
-      </c>
-      <c r="C17" s="110"/>
+      <c r="A17" s="123"/>
+      <c r="B17" s="130"/>
+      <c r="C17" s="130"/>
       <c r="D17" s="69"/>
       <c r="E17" s="72"/>
       <c r="F17" s="74"/>
-      <c r="G17" s="109"/>
-      <c r="H17" s="110"/>
+      <c r="G17" s="128" t="s">
+        <v>80</v>
+      </c>
+      <c r="H17" s="129"/>
       <c r="I17" s="99"/>
       <c r="J17" s="27"/>
       <c r="K17" s="27"/>
     </row>
     <row r="18" spans="1:11" ht="75.75" customHeight="1">
-      <c r="A18" s="107"/>
+      <c r="A18" s="118"/>
       <c r="B18" s="75"/>
       <c r="C18" s="76"/>
       <c r="D18" s="81"/>
       <c r="E18" s="82"/>
       <c r="F18" s="74"/>
-      <c r="G18" s="109"/>
-      <c r="H18" s="110"/>
+      <c r="G18" s="111"/>
+      <c r="H18" s="112"/>
       <c r="I18" s="69"/>
       <c r="K18" s="27"/>
     </row>
@@ -1860,14 +1873,14 @@
       <c r="K19" s="27"/>
     </row>
     <row r="20" spans="1:11" ht="53.25" customHeight="1">
-      <c r="A20" s="106" t="s">
+      <c r="A20" s="117" t="s">
         <v>14</v>
       </c>
-      <c r="B20" s="97" t="s">
-        <v>73</v>
-      </c>
-      <c r="C20" s="80" t="s">
-        <v>70</v>
+      <c r="B20" s="126" t="s">
+        <v>71</v>
+      </c>
+      <c r="C20" s="126" t="s">
+        <v>72</v>
       </c>
       <c r="F20" s="34"/>
       <c r="G20" s="32"/>
@@ -1877,8 +1890,7 @@
       <c r="K20" s="27"/>
     </row>
     <row r="21" spans="1:11" ht="56.25" customHeight="1">
-      <c r="A21" s="107"/>
-      <c r="B21" s="68"/>
+      <c r="A21" s="118"/>
       <c r="C21" s="68"/>
       <c r="D21" s="80"/>
       <c r="E21" s="80"/>
@@ -1920,10 +1932,10 @@
       <c r="G23" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="H23" s="118" t="s">
+      <c r="H23" s="115" t="s">
         <v>18</v>
       </c>
-      <c r="I23" s="118"/>
+      <c r="I23" s="115"/>
       <c r="J23" s="27"/>
       <c r="K23" s="27"/>
     </row>
@@ -1945,7 +1957,7 @@
         <v>36</v>
       </c>
       <c r="I24" s="90" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J24" s="27"/>
       <c r="K24" s="27"/>
@@ -1968,7 +1980,7 @@
         <v>37</v>
       </c>
       <c r="I25" s="90" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J25" s="27"/>
       <c r="K25" s="27"/>
@@ -1991,7 +2003,7 @@
         <v>38</v>
       </c>
       <c r="I26" s="101" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="J26" s="27"/>
       <c r="K26" s="27"/>
@@ -1999,10 +2011,10 @@
     <row r="27" spans="1:11" ht="15.75" customHeight="1" thickBot="1">
       <c r="A27" s="42"/>
       <c r="B27" s="86" t="s">
+        <v>50</v>
+      </c>
+      <c r="C27" s="85" t="s">
         <v>51</v>
-      </c>
-      <c r="C27" s="85" t="s">
-        <v>52</v>
       </c>
       <c r="D27" s="25"/>
       <c r="E27" s="43"/>
@@ -2033,7 +2045,7 @@
         <v>40</v>
       </c>
       <c r="I28" s="90" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J28" s="27"/>
       <c r="K28" s="27"/>
@@ -2041,10 +2053,10 @@
     <row r="29" spans="1:11" ht="15.75" customHeight="1" thickBot="1">
       <c r="A29" s="42"/>
       <c r="B29" s="86" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C29" s="85" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D29" s="25"/>
       <c r="E29" s="45"/>
@@ -2056,7 +2068,7 @@
         <v>41</v>
       </c>
       <c r="I29" s="92" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J29" s="27"/>
       <c r="K29" s="27"/>
@@ -2064,10 +2076,10 @@
     <row r="30" spans="1:11" ht="15.75" customHeight="1" thickBot="1">
       <c r="A30" s="42"/>
       <c r="B30" s="86" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C30" s="85" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D30" s="66"/>
       <c r="E30" s="45"/>
@@ -2079,7 +2091,7 @@
         <v>42</v>
       </c>
       <c r="I30" s="92" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="J30" s="27"/>
       <c r="K30" s="27"/>
@@ -2087,10 +2099,10 @@
     <row r="31" spans="1:11" ht="15.75" customHeight="1" thickBot="1">
       <c r="A31" s="42"/>
       <c r="B31" s="86" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C31" s="85" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D31" s="66"/>
       <c r="E31" s="45"/>
@@ -2102,7 +2114,7 @@
         <v>43</v>
       </c>
       <c r="I31" s="92" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="J31" s="27"/>
       <c r="K31" s="27"/>
@@ -2110,10 +2122,10 @@
     <row r="32" spans="1:11" ht="15.75" customHeight="1" thickBot="1">
       <c r="A32" s="42"/>
       <c r="B32" s="86" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C32" s="85" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="D32" s="25"/>
       <c r="E32" s="45"/>
@@ -2125,7 +2137,7 @@
         <v>44</v>
       </c>
       <c r="I32" s="92" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J32" s="27"/>
       <c r="K32" s="27"/>
@@ -2133,10 +2145,10 @@
     <row r="33" spans="1:24" ht="15.75" customHeight="1" thickBot="1">
       <c r="A33" s="47"/>
       <c r="B33" s="86" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C33" s="86" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="D33" s="25"/>
       <c r="E33" s="45"/>
@@ -2148,7 +2160,7 @@
         <v>45</v>
       </c>
       <c r="I33" s="93" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J33" s="27"/>
       <c r="K33" s="27"/>
@@ -2159,8 +2171,8 @@
       <c r="E34" s="45"/>
       <c r="F34" s="46"/>
       <c r="G34" s="67"/>
-      <c r="H34" s="119"/>
-      <c r="I34" s="119"/>
+      <c r="H34" s="116"/>
+      <c r="I34" s="116"/>
       <c r="J34" s="27"/>
       <c r="K34" s="27"/>
     </row>
@@ -2170,8 +2182,8 @@
       <c r="E35" s="45"/>
       <c r="F35" s="46"/>
       <c r="G35" s="67"/>
-      <c r="H35" s="119"/>
-      <c r="I35" s="119"/>
+      <c r="H35" s="116"/>
+      <c r="I35" s="116"/>
       <c r="J35" s="27"/>
       <c r="K35" s="27"/>
     </row>
@@ -2209,8 +2221,8 @@
       </c>
     </row>
     <row r="39" spans="1:24" ht="15.75" customHeight="1">
-      <c r="A39" s="117"/>
-      <c r="B39" s="117"/>
+      <c r="A39" s="114"/>
+      <c r="B39" s="114"/>
       <c r="C39" s="6"/>
       <c r="D39" s="6"/>
       <c r="E39" s="6"/>
@@ -3992,37 +4004,36 @@
     <row r="993" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="H11:I11"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="H34:I34"/>
     <mergeCell ref="A7:A8"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="H35:I35"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A16:A18"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="A13:A14"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="51" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
-  <rowBreaks count="3" manualBreakCount="3">
-    <brk id="27" max="16383" man="1"/>
-    <brk id="37" max="16383" man="1"/>
-    <brk id="40" max="16383" man="1"/>
+  <rowBreaks count="2" manualBreakCount="2">
+    <brk id="35" max="16383" man="1"/>
+    <brk id="48" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>